--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/player_0.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/player_0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SharedFolder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714561D1-499B-4D21-B5D9-FC9174C0A658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBBD5CC-F8D2-4B77-AB4C-3D1834667385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6630" yWindow="2265" windowWidth="19380" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1665" windowWidth="19395" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes_base" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="22">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -63,18 +63,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이동속도 1 증가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동속도 2 증가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동속도 5 증가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HealthRecovery</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -116,6 +104,10 @@
   </si>
   <si>
     <t>Lucky</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도 0.01 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -493,7 +485,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -501,7 +493,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -509,7 +501,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -517,7 +509,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -525,7 +517,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -533,7 +525,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -541,7 +533,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -553,7 +545,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -564,7 +556,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -576,7 +568,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -584,7 +576,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -598,7 +590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3CE5BFE-EF2D-4BBF-853C-AFB047A960B0}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="24.625" customWidth="1"/>
@@ -628,7 +620,7 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -637,7 +629,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1"/>
     </row>
@@ -646,7 +638,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>0.01</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -655,7 +647,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1"/>
     </row>
@@ -664,7 +656,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0.01</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -673,26 +665,318 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1"/>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.01</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.01</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.01</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1">
+        <v>30</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>0.01</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1">
+        <v>35</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>0.01</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1">
+        <v>40</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>0.01</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1">
+        <v>45</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>0.01</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1">
+        <v>50</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>0.01</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1">
+        <v>55</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>0.01</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1">
+        <v>60</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>0.01</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1">
+        <v>65</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>0.01</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1">
+        <v>70</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>0.01</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1">
+        <v>75</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>0.01</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1">
+        <v>80</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>0.01</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="1">
+        <v>85</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>0.01</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1">
+        <v>90</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>0.01</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="1">
+        <v>95</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>0.01</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="1">
+        <v>100</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>0.01</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1">
+        <v>105</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/player_0.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/player_0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mokju\forgit\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBBD5CC-F8D2-4B77-AB4C-3D1834667385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ED4C4E-8331-4203-88B8-AFA0CCD1905D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1665" windowWidth="19395" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes_base" sheetId="1" r:id="rId1"/>
@@ -620,7 +620,7 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/player_0.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/player_0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mokju\forgit\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ED4C4E-8331-4203-88B8-AFA0CCD1905D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE1EB8E-2D35-4112-B224-DF3C11DB0C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33315" yWindow="1230" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes_base" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="25">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -108,6 +108,18 @@
   </si>
   <si>
     <t>이동속도 0.01 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxSpellCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellCooldown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellAutoRechargeTime</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -431,7 +443,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24.625" customWidth="1"/>
@@ -580,6 +592,30 @@
       </c>
       <c r="B15">
         <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
